--- a/PTBR/Lang/PTBR/Dialog/Drama/guild_master_thief.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/guild_master_thief.xlsx
@@ -427,7 +427,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>... Você quer morrer?</t>
+          <t>...Você quer morrer.</t>
         </is>
       </c>
     </row>
